--- a/data/trans_camb/IP04D$colectiva-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Provincia-trans_camb.xlsx
@@ -581,7 +581,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 0,0</t>
+          <t>-6,91; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 0,93</t>
+          <t>-5,84; 0,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 0,0</t>
+          <t>-3,81; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 5,44</t>
+          <t>-1,81; 5,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; -0,46</t>
+          <t>-3,83; -0,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,22</t>
+          <t>-2,66; 1,87</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 0,51</t>
+          <t>-4,9; 0,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,15</t>
+          <t>-2,35; 4,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 0,83</t>
+          <t>-5,24; 1,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,24</t>
+          <t>-4,62; 2,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 0,07</t>
+          <t>-3,76; 0,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,16</t>
+          <t>-2,59; 2,02</t>
         </is>
       </c>
     </row>
@@ -866,34 +866,34 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>-78,14; —</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 286,6</t>
+          <t>-100,0; 430,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,72; 54,22</t>
+          <t>-100,0; 41,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,41; 191,84</t>
+          <t>-72,02; 169,4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 6,29</t>
+          <t>-3,1; 5,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 18,15</t>
+          <t>3,87; 17,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 5,71</t>
+          <t>-1,04; 5,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,48; 26,6</t>
+          <t>10,97; 27,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,0</t>
+          <t>-1,15; 4,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,88; 20,09</t>
+          <t>9,06; 20,3</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,78; —</t>
+          <t>33,42; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,97; 1364,73</t>
+          <t>-73,18; 844,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>204,82; 3420,99</t>
+          <t>240,77; 3723,37</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 3,12</t>
+          <t>-10,57; 2,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 13,82</t>
+          <t>-3,18; 13,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 8,51</t>
+          <t>-3,48; 8,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 7,58</t>
+          <t>-5,02; 7,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 4,25</t>
+          <t>-4,86; 3,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 8,71</t>
+          <t>-2,33; 8,66</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-83,89; 99,46</t>
+          <t>-83,38; 96,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 324,65</t>
+          <t>-36,73; 301,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-82,18; 855,57</t>
+          <t>-81,62; 708,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,82; 120,32</t>
+          <t>-63,29; 121,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,91; 251,35</t>
+          <t>-37,46; 238,35</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-19,91; -3,55</t>
+          <t>-20,72; -3,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-19,59; -3,17</t>
+          <t>-21,57; -4,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-25,76; -6,93</t>
+          <t>-24,88; -7,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-25,5; -7,22</t>
+          <t>-24,58; -7,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-19,82; -7,24</t>
+          <t>-18,75; -6,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -7,11</t>
+          <t>-18,84; -6,86</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,23; 23,05</t>
+          <t>3,43; 23,5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>25,55; 50,13</t>
+          <t>24,84; 49,93</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8,2; 27,76</t>
+          <t>7,9; 26,51</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21,07; 43,18</t>
+          <t>21,88; 43,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,59; 22,37</t>
+          <t>7,73; 22,85</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,68; 42,72</t>
+          <t>26,86; 42,81</t>
         </is>
       </c>
     </row>
@@ -1485,39 +1485,39 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2,1; 810,53</t>
+          <t>20,61; 933,7</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>195,83; 1723,68</t>
+          <t>188,59; 1955,29</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>77,62; 2103,33</t>
+          <t>93,15; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>196,9; 3249,88</t>
+          <t>274,34; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>80,84; 764,51</t>
+          <t>85,91; 814,07</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>304,97; 1600,87</t>
+          <t>284,54; 1597,64</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,78</t>
+          <t>-0,87; 6,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,5; 13,69</t>
+          <t>4,01; 13,67</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,93; 6,42</t>
+          <t>0,74; 5,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,25; 12,64</t>
+          <t>4,5; 12,5</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,93</t>
+          <t>0,73; 5,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,11; 11,62</t>
+          <t>5,42; 11,46</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 1021,5</t>
+          <t>-49,18; 1440,41</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>62,83; 2208,05</t>
+          <t>87,25; 2353,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,36; 1367,39</t>
+          <t>11,63; 1041,3</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>209,49; 3172,86</t>
+          <t>242,02; 3110,94</t>
         </is>
       </c>
     </row>
@@ -1721,32 +1721,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 1,06</t>
+          <t>-3,46; 1,21</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -0,86</t>
+          <t>-4,8; -0,86</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,35</t>
+          <t>-4,4; 0,41</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,71; -0,36</t>
+          <t>-4,71; -0,38</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,02</t>
+          <t>-3,18; 0,05</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,86; -1,05</t>
+          <t>-3,92; -1,01</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 153,9</t>
+          <t>-95,83; 153,96</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1807,22 +1807,22 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 143,68</t>
+          <t>-100,0; 166,63</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 146,83</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-89,36; 16,05</t>
+          <t>-89,15; 26,28</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -22,32</t>
+          <t>-100,0; -36,91</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1877,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,66</t>
+          <t>-1,6; 1,7</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,73</t>
+          <t>2,24; 6,59</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,21</t>
+          <t>-0,69; 2,29</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,01</t>
+          <t>2,38; 6,22</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,52</t>
+          <t>-0,73; 1,47</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,64</t>
+          <t>2,77; 5,67</t>
         </is>
       </c>
     </row>
@@ -1953,32 +1953,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 63,35</t>
+          <t>-36,91; 63,78</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>52,26; 235,81</t>
+          <t>47,36; 232,28</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 97,73</t>
+          <t>-20,63; 107,8</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>54,51; 283,88</t>
+          <t>62,03; 279,0</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 60,75</t>
+          <t>-19,49; 55,22</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>77,71; 211,51</t>
+          <t>77,47; 219,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$colectiva-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Provincia-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 0,0</t>
+          <t>-6,75; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 0,83</t>
+          <t>-5,47; 1,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,0</t>
+          <t>-5,63; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 5,29</t>
+          <t>-1,8; 5,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; -0,46</t>
+          <t>-3,81; -0,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,87</t>
+          <t>-2,41; 1,94</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 0,55</t>
+          <t>-4,36; 0,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 4,53</t>
+          <t>-2,39; 4,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 1,23</t>
+          <t>-5,11; 1,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 2,29</t>
+          <t>-4,39; 2,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,26</t>
+          <t>-3,69; 0,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 2,02</t>
+          <t>-2,67; 1,91</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-78,14; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 230,42</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 430,86</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 41,39</t>
+          <t>-100,0; 96,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,02; 169,4</t>
+          <t>-76,32; 169,01</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 5,46</t>
+          <t>-3,17; 5,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 17,94</t>
+          <t>4,22; 18,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 5,74</t>
+          <t>-1,04; 6,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,97; 27,55</t>
+          <t>9,69; 26,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,56</t>
+          <t>-1,08; 4,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,06; 20,3</t>
+          <t>8,49; 19,76</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>25,38; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>33,42; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,18; 844,77</t>
+          <t>-72,95; 917,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>240,77; 3723,37</t>
+          <t>174,33; 3511,32</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 2,91</t>
+          <t>-10,75; 2,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 13,72</t>
+          <t>-3,17; 14,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 8,28</t>
+          <t>-3,61; 7,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 7,33</t>
+          <t>-4,87; 7,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 3,7</t>
+          <t>-5,16; 4,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 8,66</t>
+          <t>-2,28; 8,17</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-83,38; 96,65</t>
+          <t>-82,56; 102,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,73; 301,31</t>
+          <t>-34,32; 313,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,62; 708,59</t>
+          <t>-81,95; 825,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>-100,0; 967,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-63,29; 121,33</t>
+          <t>-63,71; 113,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,46; 238,35</t>
+          <t>-32,87; 225,11</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,72; -3,71</t>
+          <t>-19,95; -3,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-21,57; -4,44</t>
+          <t>-19,81; -4,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-24,88; -7,43</t>
+          <t>-25,17; -7,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,58; -7,28</t>
+          <t>-24,09; -7,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,75; -6,77</t>
+          <t>-18,31; -6,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,84; -6,86</t>
+          <t>-18,17; -7,02</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,43; 23,5</t>
+          <t>3,05; 23,47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>24,84; 49,93</t>
+          <t>24,96; 49,08</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7,9; 26,51</t>
+          <t>6,98; 27,39</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21,88; 43,02</t>
+          <t>21,93; 43,93</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,73; 22,85</t>
+          <t>8,13; 22,57</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,86; 42,81</t>
+          <t>26,07; 42,53</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1485,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20,61; 933,7</t>
+          <t>2,6; 798,02</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>188,59; 1955,29</t>
+          <t>198,61; 1833,46</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>93,15; —</t>
+          <t>38,28; 1969,71</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>274,34; —</t>
+          <t>185,55; 3141,2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>85,91; 814,07</t>
+          <t>93,83; 837,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>284,54; 1597,64</t>
+          <t>297,24; 1896,45</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 6,0</t>
+          <t>-0,56; 5,97</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4,01; 13,67</t>
+          <t>3,56; 13,56</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,74; 5,89</t>
+          <t>0,64; 6,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,5; 12,5</t>
+          <t>4,59; 12,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,18</t>
+          <t>0,82; 5,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,42; 11,46</t>
+          <t>5,31; 11,81</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 1440,41</t>
+          <t>-45,57; 1112,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>87,25; 2353,45</t>
+          <t>70,53; 2098,93</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>11,63; 1041,3</t>
+          <t>17,39; 1397,56</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>242,02; 3110,94</t>
+          <t>211,32; 3069,51</t>
         </is>
       </c>
     </row>
@@ -1721,32 +1721,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,21</t>
+          <t>-3,55; 1,21</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,8; -0,86</t>
+          <t>-4,44; -0,77</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,41</t>
+          <t>-4,65; -0,01</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,71; -0,38</t>
+          <t>-5,1; -0,41</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,05</t>
+          <t>-3,29; 0,05</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,92; -1,01</t>
+          <t>-3,88; -0,94</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-95,83; 153,96</t>
+          <t>-100,0; 168,79</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1807,22 +1807,22 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 166,63</t>
+          <t>-100,0; 80,83</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,83</t>
+          <t>-100,0; 29,36</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-89,15; 26,28</t>
+          <t>-89,48; 17,35</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -36,91</t>
+          <t>-100,0; -12,73</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1877,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,7</t>
+          <t>-1,6; 1,81</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,59</t>
+          <t>2,27; 6,56</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,29</t>
+          <t>-0,65; 2,25</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,22</t>
+          <t>2,19; 5,91</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,47</t>
+          <t>-0,61; 1,55</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,67</t>
+          <t>2,93; 5,72</t>
         </is>
       </c>
     </row>
@@ -1953,32 +1953,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 63,78</t>
+          <t>-36,68; 69,46</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>47,36; 232,28</t>
+          <t>50,18; 236,95</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 107,8</t>
+          <t>-19,65; 110,08</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>62,03; 279,0</t>
+          <t>60,33; 277,57</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 55,22</t>
+          <t>-17,33; 59,2</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>77,47; 219,1</t>
+          <t>74,45; 210,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$colectiva-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Provincia-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción colectiva en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-2,01</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,9</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,63</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 0,0</t>
+          <t>-4,46; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 1,23</t>
+          <t>-2,86; 1,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 0,0</t>
+          <t>-6,19; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 5,36</t>
+          <t>-5,07; 1,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -0,46</t>
+          <t>-3,85; -0,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,94</t>
+          <t>-3,02; 1,09</t>
         </is>
       </c>
     </row>
@@ -672,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-62,08%</t>
+          <t>-16,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -682,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>-58,37%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-23,64%</t>
+          <t>-44,15%</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,22</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-1,33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,32</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,53</t>
+          <t>-5,12; 0,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 4,44</t>
+          <t>-4,36; 2,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 1,19</t>
+          <t>-4,3; 0,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,29</t>
+          <t>-1,97; 6,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,23</t>
+          <t>-3,57; 0,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,91</t>
+          <t>-2,46; 2,83</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-58,54%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-41,96%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-70,82%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>33,16%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-58,54%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-45,18%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-14,95%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -866,12 +868,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 307,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 230,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -881,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,8</t>
+          <t>-91,72; 54,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-76,32; 169,01</t>
+          <t>-74,1; 235,49</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,86</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17,27</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>1,12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>10,13</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,86</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,24</t>
+          <t>10,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,91</t>
+          <t>13,96</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 5,6</t>
+          <t>-1,1; 5,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 18,74</t>
+          <t>9,62; 26,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 6,49</t>
+          <t>-2,99; 6,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,69; 26,31</t>
+          <t>4,11; 18,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,54</t>
+          <t>-1,29; 5,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,49; 19,76</t>
+          <t>9,04; 19,95</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>190,15%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1764,95%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>54,78%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>496,46%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>190,15%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1762,15%</t>
+          <t>514,34%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>928,95%</t>
+          <t>932,35%</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1019,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,38; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1032,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,2; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-72,95; 917,28</t>
+          <t>-64,97; 1364,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>174,33; 3511,32</t>
+          <t>220,48; 3447,04</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,52</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,46</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-3,22</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4,68</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,52</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>3,21</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 2,98</t>
+          <t>-3,33; 8,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 14,54</t>
+          <t>-4,02; 8,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 7,91</t>
+          <t>-10,37; 3,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 7,76</t>
+          <t>-3,66; 14,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 4,07</t>
+          <t>-4,95; 4,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 8,17</t>
+          <t>-2,14; 9,79</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>76,26%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44,21%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-40,14%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>58,35%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>76,26%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>57,48%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-82,56; 102,1</t>
+          <t>-82,18; 855,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 313,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,95; 825,47</t>
+          <t>-83,89; 99,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 967,79</t>
+          <t>-36,06; 333,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-63,71; 113,63</t>
+          <t>-57,82; 120,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,87; 225,11</t>
+          <t>-32,46; 267,25</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-14,09</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-14,09</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-9,91</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-9,91</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-14,09</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-14,09</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-19,95; -3,24</t>
+          <t>-25,76; -6,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-19,81; -4,52</t>
+          <t>-25,5; -7,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-25,17; -7,12</t>
+          <t>-19,91; -3,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,09; -7,21</t>
+          <t>-19,59; -3,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,31; -6,92</t>
+          <t>-19,82; -7,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,17; -7,02</t>
+          <t>-18,93; -7,11</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>16,97</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>31,53</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>12,69</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>37,12</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>16,97</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32,26</t>
+          <t>36,94</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1396,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,37</t>
+          <t>34,16</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,05; 23,47</t>
+          <t>8,2; 27,76</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>24,96; 49,08</t>
+          <t>20,49; 42,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,98; 27,39</t>
+          <t>2,23; 23,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21,93; 43,93</t>
+          <t>25,33; 50,51</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,13; 22,57</t>
+          <t>7,59; 22,37</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,07; 42,53</t>
+          <t>25,95; 42,2</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>465,42%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>865,03%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>192,93%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>564,25%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>465,42%</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>884,96%</t>
+          <t>561,59%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1472,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>680,75%</t>
+          <t>676,6%</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2,6; 798,02</t>
+          <t>77,62; 2103,33</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>198,61; 1833,46</t>
+          <t>190,17; 3174,56</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>38,28; 1969,71</t>
+          <t>2,1; 810,53</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>185,55; 3141,2</t>
+          <t>184,53; 1729,36</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>93,83; 837,79</t>
+          <t>80,84; 764,51</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>297,24; 1896,45</t>
+          <t>300,38; 1590,64</t>
         </is>
       </c>
     </row>
@@ -1527,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3,03</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>8,87</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>2,33</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>8,23</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3,03</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7,98</t>
+          <t>8,96</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1552,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,04</t>
+          <t>8,88</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,97</t>
+          <t>0,93; 6,42</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,56; 13,56</t>
+          <t>4,87; 13,88</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,44</t>
+          <t>-0,66; 5,78</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,59; 12,85</t>
+          <t>3,95; 14,84</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,25</t>
+          <t>0,66; 4,93</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,31; 11,81</t>
+          <t>5,78; 12,71</t>
         </is>
       </c>
     </row>
@@ -1603,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>654,79%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1917,42%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>139,86%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>493,25%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>654,79%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1725,17%</t>
+          <t>536,5%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1628,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>765,06%</t>
+          <t>845,12%</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 1112,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>70,53; 2098,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-44,16; 1021,5</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>65,36; 2408,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>17,39; 1397,56</t>
+          <t>7,36; 1367,39</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>211,32; 3069,51</t>
+          <t>240,33; 3446,45</t>
         </is>
       </c>
     </row>
@@ -1683,24 +1685,24 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-1,71</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-2,19</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-1,08</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-2,31</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-2,1</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-1,4</t>
@@ -1708,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-2,24</t>
         </is>
       </c>
     </row>
@@ -1721,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,21</t>
+          <t>-4,36; 0,35</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,44; -0,77</t>
+          <t>-4,83; -0,5</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,65; -0,01</t>
+          <t>-3,72; 1,06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -0,41</t>
+          <t>-4,94; -0,86</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,05</t>
+          <t>-3,21; -0,02</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,88; -0,94</t>
+          <t>-3,95; -1,16</t>
         </is>
       </c>
     </row>
@@ -1759,24 +1761,24 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-67,73%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-86,96%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-46,85%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-67,73%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-83,28%</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-57,94%</t>
@@ -1784,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-90,54%</t>
+          <t>-92,79%</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1799,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 168,79</t>
+          <t>-100,0; 143,68</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1807,22 +1809,22 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 80,83</t>
+          <t>-100,0; 153,9</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-89,48; 17,35</t>
+          <t>-89,36; 16,05</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -12,73</t>
+          <t>-100,0; -40,54</t>
         </is>
       </c>
     </row>
@@ -1839,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>4,01</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-0,03</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>4,33</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1864,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>4,43</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,81</t>
+          <t>-0,88; 2,21</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,56</t>
+          <t>2,1; 5,87</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,25</t>
+          <t>-1,47; 1,66</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,91</t>
+          <t>2,84; 7,25</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,55</t>
+          <t>-0,79; 1,52</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,72</t>
+          <t>3,05; 5,84</t>
         </is>
       </c>
     </row>
@@ -1915,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>27,03%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>143,91%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>-0,99%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>123,79%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>148,91%</t>
+          <t>140,44%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1940,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>134,77%</t>
+          <t>141,43%</t>
         </is>
       </c>
     </row>
@@ -1953,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 69,46</t>
+          <t>-26,99; 97,73</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>50,18; 236,95</t>
+          <t>53,57; 282,74</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 110,08</t>
+          <t>-36,12; 63,35</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>60,33; 277,57</t>
+          <t>65,51; 258,1</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 59,2</t>
+          <t>-21,67; 60,75</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>74,45; 210,8</t>
+          <t>79,73; 221,19</t>
         </is>
       </c>
     </row>
